--- a/crates/xlstream-eval/tests/fixtures/financial/npv.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/financial/npv.xlsx
@@ -20,18 +20,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">val</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">npv</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t xml:space="preserve">rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cf5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npv_result</t>
   </si>
 </sst>
 </file>
@@ -309,7 +318,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -325,155 +334,158 @@
       <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>3.5</v>
+        <v>-1000</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <f aca="false">NPV(0.1,A2,B2,C2)</f>
-        <v>763.298271975958</v>
+        <v>300</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <f aca="false">NPV(A2,B2,C2,D2,E2,F2)</f>
+        <v>105.059887861609</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>0.08</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>7.2</v>
+        <v>-5000</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <f aca="false">NPV(0.1,A3,B3,C3)</f>
-        <v>1906.96468820436</v>
+        <v>1500</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <f aca="false">NPV(A3,B3,C3,D3,E3,F3)</f>
+        <v>-29.4534629013911</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <f aca="false">NPV(0.1,A4,B4,C4)</f>
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <f aca="false">NPV(A4,B4,C4,D4,E4,F4)</f>
+        <v>1256.63934364013</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>100</v>
+        <v>0.12</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>15.8</v>
+        <v>-2000</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <f aca="false">NPV(0.1,A5,B5,C5)</f>
-        <v>3860.54094665665</v>
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <f aca="false">NPV(A5,B5,C5,D5,E5,F5)</f>
+        <v>3888.55427147171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>-2.3</v>
+        <v>100</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>150</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <f aca="false">NPV(0.1,A6,B6,C6)</f>
-        <v>106.250939143501</v>
+        <v>100</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <f aca="false">NPV(A6,B6,C6,D6,E6,F6)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>0.15</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>8.1</v>
+        <v>-500</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <f aca="false">NPV(0.1,A7,B7,C7)</f>
-        <v>2306.09316303531</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>75</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <f aca="false">NPV(0.1,A8,B8,C8)</f>
-        <v>5706.84447783621</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <f aca="false">NPV(0.1,A9,B9,C9)</f>
-        <v>189.151014274981</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>999</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <f aca="false">NPV(0.1,A10,B10,C10)</f>
-        <v>3923.68895567243</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>42</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <f aca="false">NPV(0.1,A11,B11,C11)</f>
-        <v>945.296769346356</v>
+        <v>-200</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <f aca="false">NPV(A7,B7,C7,D7,E7,F7)</f>
+        <v>506.534533662982</v>
       </c>
     </row>
   </sheetData>
